--- a/Appendix files/timeliste bachelor oppgave.xlsx
+++ b/Appendix files/timeliste bachelor oppgave.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\brage\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4586815-CD19-4B0A-98C4-5510D9A735AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1532C510-BEEE-40FE-872F-4691F8463864}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="660" xr2:uid="{FDA5BF7B-9CD0-4983-ACA0-DC79ECBA6415}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" firstSheet="1" activeTab="19" xr2:uid="{FDA5BF7B-9CD0-4983-ACA0-DC79ECBA6415}"/>
   </bookViews>
   <sheets>
     <sheet name="Oppsummering" sheetId="1" r:id="rId1"/>
@@ -2438,19 +2438,19 @@
       </c>
       <c r="C22" s="14">
         <f>'Uke 20'!C38</f>
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D22" s="14">
         <f>'Uke 20'!C57</f>
-        <v>39.5</v>
+        <v>42.5</v>
       </c>
       <c r="E22" s="16">
         <f t="shared" si="1"/>
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G22">
         <f t="shared" si="2"/>
-        <v>42</v>
+        <v>43.666666666666664</v>
       </c>
       <c r="I22" t="s">
         <v>11</v>
@@ -2469,19 +2469,19 @@
       </c>
       <c r="C23" s="16">
         <f t="shared" ref="C23:D23" si="3">SUM(C4:C22)</f>
-        <v>339.3</v>
+        <v>341.3</v>
       </c>
       <c r="D23" s="16">
         <f t="shared" si="3"/>
-        <v>397.5</v>
+        <v>400.5</v>
       </c>
       <c r="E23" s="16">
         <f>SUM(E4:E22)</f>
-        <v>1058.8</v>
+        <v>1063.8</v>
       </c>
       <c r="G23" s="4">
         <f>G9+G10+G11+G12+G14+G15+G13+G16+G18+G17+G19+G20+G21+G22+G8+G7+G6+G5+G4</f>
-        <v>352.93333333333339</v>
+        <v>354.6</v>
       </c>
       <c r="H23" s="4" t="s">
         <v>14</v>
@@ -7656,7 +7656,7 @@
       </c>
       <c r="B37" s="1"/>
       <c r="C37" s="6">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" spans="1:6" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -7667,7 +7667,7 @@
       <c r="B38" s="2"/>
       <c r="C38" s="7">
         <f>SUM(C24:C37)</f>
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F38" s="5"/>
     </row>
@@ -7838,7 +7838,7 @@
         <v>333</v>
       </c>
       <c r="C56" s="6">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="57" spans="1:6" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -7849,7 +7849,7 @@
       <c r="B57" s="2"/>
       <c r="C57" s="7">
         <f>SUM(C43:C56)</f>
-        <v>39.5</v>
+        <v>42.5</v>
       </c>
       <c r="F57" s="5"/>
     </row>
